--- a/radii.xlsx
+++ b/radii.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/imac/Downloads/cif-bond-analyzer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emiljaffal/Documents/GitHub/cif-bond-analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F64F90C-80BD-E048-859C-AE2B21DF4935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688FEF40-9E89-1E43-9C0C-0A6C1BCEDD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="24700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10140" yWindow="760" windowWidth="20100" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="backup_data_(not_used)" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>Element</t>
   </si>
@@ -144,13 +157,115 @@
   </si>
   <si>
     <t>Radius</t>
+  </si>
+  <si>
+    <t>Cd</t>
+  </si>
+  <si>
+    <t>Ag</t>
+  </si>
+  <si>
+    <t>As</t>
+  </si>
+  <si>
+    <t>Au</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Ba</t>
+  </si>
+  <si>
+    <t>Be</t>
+  </si>
+  <si>
+    <t>Bi</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Ca</t>
+  </si>
+  <si>
+    <t>Cr</t>
+  </si>
+  <si>
+    <t>Cs</t>
+  </si>
+  <si>
+    <t>Cu</t>
+  </si>
+  <si>
+    <t>Hg</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>Mg</t>
+  </si>
+  <si>
+    <t>Mn</t>
+  </si>
+  <si>
+    <t>Na</t>
+  </si>
+  <si>
+    <t>Nb</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Pb</t>
+  </si>
+  <si>
+    <t>Rb</t>
+  </si>
+  <si>
+    <t>Re</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Se</t>
+  </si>
+  <si>
+    <t>Sr</t>
+  </si>
+  <si>
+    <t>Te</t>
+  </si>
+  <si>
+    <t>Ti</t>
+  </si>
+  <si>
+    <t>Tl</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Zn</t>
+  </si>
+  <si>
+    <t>Zr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +278,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -200,13 +322,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,11 +635,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="2"/>
-    <col min="2" max="2" width="20.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -526,299 +651,571 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>1.1759999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>1.641</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>1.242</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>1.25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>1.246</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>1.2430000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>1.2250000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>1.7829999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>1.3240000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>1.345</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>1.3759999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="3">
         <v>1.6240000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>1.5109999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>1.4339999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>1.871</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>1.819</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>1.82</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>1.8129999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>1.7929999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="3">
         <v>1.9870000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="3">
         <v>1.7869999999999999</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="3">
         <v>1.764</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="3">
         <v>1.752</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="3">
         <v>1.7450000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="3">
         <v>1.734</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="3">
         <v>1.726</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="3">
         <v>1.9390000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="3">
         <v>1.718</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="3">
         <v>1.337</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="3">
         <v>1.3560000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="3">
         <v>1.387</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="3">
         <v>1.798</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="3">
         <v>1.377</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="3">
         <v>1.31</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="3">
         <v>1.3620000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="3">
         <v>1.5634999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="3">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3">
+        <v>1.4430000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3">
+        <v>1.2470000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1.4350000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3">
+        <v>0.80700000000000005</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="3">
+        <v>1.994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" s="3">
+        <v>1.0720000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="3">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="3">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1.716</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1.204</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B50" s="3">
+        <v>1.8939999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B51" s="3">
+        <v>1.2749999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="3">
+        <v>1.823</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="3">
+        <v>1.488</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="3">
+        <v>1.587</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1.1639999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="3">
+        <v>1.6619999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="3">
+        <v>1.4259999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="3">
+        <v>1.123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1.7250000000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="3">
+        <v>1.7809999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" s="3">
+        <v>1.345</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B63" s="3">
+        <v>1.0740000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1.2370000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B65" s="3">
+        <v>1.9770000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1.417</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1.4059999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1.663</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1.3069999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" s="3">
+        <v>1.3640000000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" s="3">
+        <v>1.333</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B72" s="3">
+        <v>1.5529999999999999</v>
       </c>
     </row>
   </sheetData>
